--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-medio-llegada.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-medio-llegada.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/medio-llegada</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/medio-llegada</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,7 +319,7 @@
 </t>
   </si>
   <si>
-    <t>identifies the meaning of the extension</t>
+    <t>URL que identifica la extensión</t>
   </si>
   <si>
     <t>Source of the definition for the extension code - a logical name or a URL.</t>
@@ -338,7 +338,7 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
+    <t>Medio de llegada del paciente</t>
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
@@ -347,7 +347,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/ValueSet/vs-medio-llegada</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-medio-llegada</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -691,7 +691,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="62.6875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.53515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>

--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-medio-llegada.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-medio-llegada.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
